--- a/data/personalia/9 JR.xlsx
+++ b/data/personalia/9 JR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B787849-717A-42F3-9A50-B943D29CA7ED}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F414170-57EE-4554-8965-0D68266E5EAF}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2194,6 +2194,9 @@
       <c r="K25" s="6">
         <v>45962</v>
       </c>
+      <c r="L25" s="6">
+        <v>46084</v>
+      </c>
       <c r="M25" s="6">
         <v>20455</v>
       </c>

--- a/data/personalia/9 JR.xlsx
+++ b/data/personalia/9 JR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F414170-57EE-4554-8965-0D68266E5EAF}"/>
+  <xr:revisionPtr revIDLastSave="332" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8575BD00-6E52-474B-8977-B56C74E4C6F1}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$94</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="186">
   <si>
     <t>Wilayah</t>
   </si>
@@ -319,9 +319,6 @@
     <t>SUJANARKO</t>
   </si>
   <si>
-    <t>RYAN ADI SAPUTRA</t>
-  </si>
-  <si>
     <t>Calon Pekerja</t>
   </si>
   <si>
@@ -461,9 +458,6 @@
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 9.6 Ktg</t>
-  </si>
-  <si>
-    <t>PNC Preventif UPT Resor STL 9.6 Ktg</t>
   </si>
   <si>
     <t>PMP.231078.00910</t>
@@ -982,7 +976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T94"/>
+  <dimension ref="A1:T93"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
@@ -1084,7 +1078,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
@@ -1108,13 +1102,13 @@
         <v>49249</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O2" s="6">
         <v>46937</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R2" s="6">
         <v>46937</v>
@@ -1137,7 +1131,7 @@
         <v>38</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
@@ -1161,13 +1155,13 @@
         <v>47727</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O3" s="6">
         <v>46448</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R3" s="6">
         <v>46448</v>
@@ -1190,7 +1184,7 @@
         <v>38</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>36</v>
@@ -1214,13 +1208,13 @@
         <v>46569</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O4" s="6">
         <v>45696</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="R4" s="6">
         <v>47370</v>
@@ -1243,7 +1237,7 @@
         <v>35</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>36</v>
@@ -1267,7 +1261,7 @@
         <v>54210</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O5" s="6">
         <v>46446</v>
@@ -1290,7 +1284,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>36</v>
@@ -1314,13 +1308,13 @@
         <v>52263</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O6" s="6">
         <v>46837</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R6" s="6">
         <v>47114</v>
@@ -1343,7 +1337,7 @@
         <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>36</v>
@@ -1367,7 +1361,7 @@
         <v>54363</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O7" s="6">
         <v>46448</v>
@@ -1390,7 +1384,7 @@
         <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>36</v>
@@ -1414,7 +1408,7 @@
         <v>54210</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O8" s="6">
         <v>46610</v>
@@ -1437,10 +1431,10 @@
         <v>42</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="H9" s="6">
         <v>45597</v>
@@ -1478,10 +1472,10 @@
         <v>43</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="H10" s="6">
         <v>45658</v>
@@ -1519,10 +1513,10 @@
         <v>43</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H11" s="6">
         <v>45086</v>
@@ -1543,7 +1537,7 @@
         <v>46143</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O11" s="6">
         <v>47324</v>
@@ -1566,10 +1560,10 @@
         <v>39</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H12" s="6">
         <v>45703</v>
@@ -1590,7 +1584,7 @@
         <v>52536</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O12" s="6">
         <v>46937</v>
@@ -1613,10 +1607,10 @@
         <v>40</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H13" s="6">
         <v>45427</v>
@@ -1637,7 +1631,7 @@
         <v>52232</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O13" s="6">
         <v>47175</v>
@@ -1660,10 +1654,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H14" s="6">
         <v>45427</v>
@@ -1684,7 +1678,7 @@
         <v>53752</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O14" s="6">
         <v>46950</v>
@@ -1707,10 +1701,10 @@
         <v>41</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H15" s="6">
         <v>45139</v>
@@ -1731,7 +1725,7 @@
         <v>55366</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O15" s="6">
         <v>46950</v>
@@ -1754,10 +1748,10 @@
         <v>41</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H16" s="6">
         <v>45870</v>
@@ -1778,7 +1772,7 @@
         <v>52749</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O16" s="6">
         <v>47114</v>
@@ -1801,10 +1795,10 @@
         <v>41</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H17" s="6">
         <v>44927</v>
@@ -1825,7 +1819,7 @@
         <v>55885</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O17" s="6">
         <v>46433</v>
@@ -1848,10 +1842,10 @@
         <v>41</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H18" s="6">
         <v>45611</v>
@@ -1872,7 +1866,7 @@
         <v>55550</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O18" s="6">
         <v>46433</v>
@@ -1895,10 +1889,10 @@
         <v>41</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H19" s="6">
         <v>45611</v>
@@ -1919,7 +1913,7 @@
         <v>57589</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O19" s="6">
         <v>46916</v>
@@ -1942,10 +1936,10 @@
         <v>39</v>
       </c>
       <c r="F20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="H20" s="6">
         <v>45627</v>
@@ -1966,13 +1960,13 @@
         <v>51867</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O20" s="6">
         <v>47175</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R20" s="6">
         <v>47370</v>
@@ -1995,10 +1989,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H21" s="6">
         <v>45689</v>
@@ -2036,10 +2030,10 @@
         <v>40</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H22" s="6">
         <v>45870</v>
@@ -2060,7 +2054,7 @@
         <v>54393</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O22" s="6">
         <v>46881</v>
@@ -2083,10 +2077,10 @@
         <v>41</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H23" s="6">
         <v>44927</v>
@@ -2107,7 +2101,7 @@
         <v>55001</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O23" s="6">
         <v>46433</v>
@@ -2130,10 +2124,10 @@
         <v>41</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H24" s="6">
         <v>44927</v>
@@ -2154,7 +2148,7 @@
         <v>54820</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O24" s="6">
         <v>46433</v>
@@ -2174,13 +2168,13 @@
         <v>33</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H25" s="6">
         <v>45962</v>
@@ -2218,10 +2212,10 @@
         <v>41</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H26" s="6">
         <v>45611</v>
@@ -2242,7 +2236,7 @@
         <v>49583</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O26" s="6">
         <v>46610</v>
@@ -2266,10 +2260,10 @@
         <v>39</v>
       </c>
       <c r="F27" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="H27" s="6">
         <v>45427</v>
@@ -2290,7 +2284,7 @@
         <v>48580</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O27" s="6">
         <v>47203</v>
@@ -2313,10 +2307,10 @@
         <v>40</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H28" s="6">
         <v>45611</v>
@@ -2337,7 +2331,7 @@
         <v>54605</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O28" s="6">
         <v>47175</v>
@@ -2360,10 +2354,10 @@
         <v>40</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H29" s="6">
         <v>45870</v>
@@ -2384,7 +2378,7 @@
         <v>52597</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O29" s="6">
         <v>47203</v>
@@ -2404,13 +2398,13 @@
         <v>33</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H30" s="6">
         <v>45809</v>
@@ -2445,13 +2439,13 @@
         <v>33</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H31" s="6">
         <v>45809</v>
@@ -2489,10 +2483,10 @@
         <v>41</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H32" s="6">
         <v>44927</v>
@@ -2530,10 +2524,10 @@
         <v>41</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H33" s="6">
         <v>44927</v>
@@ -2554,7 +2548,7 @@
         <v>50072</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O33" s="6">
         <v>47265</v>
@@ -2577,10 +2571,10 @@
         <v>41</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H34" s="6">
         <v>45611</v>
@@ -2601,7 +2595,7 @@
         <v>56309</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O34" s="6">
         <v>46446</v>
@@ -2624,10 +2618,10 @@
         <v>39</v>
       </c>
       <c r="F35" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="H35" s="6">
         <v>45427</v>
@@ -2665,10 +2659,10 @@
         <v>40</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6">
         <v>45870</v>
@@ -2706,10 +2700,10 @@
         <v>40</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H37" s="6">
         <v>45731</v>
@@ -2730,7 +2724,7 @@
         <v>55579</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O37" s="6">
         <v>46446</v>
@@ -2753,10 +2747,10 @@
         <v>41</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H38" s="6">
         <v>44927</v>
@@ -2777,7 +2771,7 @@
         <v>47300</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="O38" s="6">
         <v>47175</v>
@@ -2800,10 +2794,10 @@
         <v>41</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H39" s="6">
         <v>45870</v>
@@ -2824,7 +2818,7 @@
         <v>56005</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O39" s="6">
         <v>46476</v>
@@ -2847,10 +2841,10 @@
         <v>41</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H40" s="6">
         <v>44927</v>
@@ -2871,7 +2865,7 @@
         <v>53966</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O40" s="6">
         <v>46433</v>
@@ -2894,10 +2888,10 @@
         <v>39</v>
       </c>
       <c r="F41" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="H41" s="6">
         <v>45870</v>
@@ -2918,7 +2912,7 @@
         <v>53297</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O41" s="6">
         <v>47114</v>
@@ -2941,10 +2935,10 @@
         <v>40</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H42" s="6">
         <v>45611</v>
@@ -2965,7 +2959,7 @@
         <v>54332</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O42" s="6">
         <v>47324</v>
@@ -2988,10 +2982,10 @@
         <v>40</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H43" s="6">
         <v>45689</v>
@@ -3012,7 +3006,7 @@
         <v>54636</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O43" s="6">
         <v>47114</v>
@@ -3032,13 +3026,13 @@
         <v>33</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H44" s="6">
         <v>45809</v>
@@ -3073,13 +3067,13 @@
         <v>33</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H45" s="6">
         <v>45809</v>
@@ -3117,10 +3111,10 @@
         <v>41</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H46" s="6">
         <v>45611</v>
@@ -3141,7 +3135,7 @@
         <v>55916</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O46" s="6">
         <v>46433</v>
@@ -3164,10 +3158,10 @@
         <v>39</v>
       </c>
       <c r="F47" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="H47" s="6">
         <v>45870</v>
@@ -3188,13 +3182,13 @@
         <v>53297</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="O47" s="6">
         <v>47114</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R47" s="6">
         <v>47370</v>
@@ -3217,10 +3211,10 @@
         <v>40</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H48" s="6">
         <v>45731</v>
@@ -3258,10 +3252,10 @@
         <v>40</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H49" s="6">
         <v>45427</v>
@@ -3282,7 +3276,7 @@
         <v>53144</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O49" s="6">
         <v>47324</v>
@@ -3305,10 +3299,10 @@
         <v>41</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H50" s="6">
         <v>44927</v>
@@ -3329,7 +3323,7 @@
         <v>54363</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O50" s="6">
         <v>46837</v>
@@ -3352,10 +3346,10 @@
         <v>41</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H51" s="6">
         <v>44927</v>
@@ -3376,7 +3370,7 @@
         <v>56309</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="O51" s="6">
         <v>46433</v>
@@ -3399,10 +3393,10 @@
         <v>41</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H52" s="6">
         <v>45611</v>
@@ -3423,52 +3417,14 @@
         <v>52536</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6">
         <v>47114</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C53" s="2">
-        <v>77811</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H53" s="6">
-        <v>45809</v>
-      </c>
-      <c r="I53" s="2">
-        <v>4</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K53" s="6">
-        <v>45689</v>
-      </c>
-      <c r="L53" s="6">
-        <v>46084</v>
-      </c>
-      <c r="M53" s="6">
-        <v>20455</v>
-      </c>
+      <c r="D53" s="2"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.45">
       <c r="D54" s="2"/>
@@ -3522,19 +3478,19 @@
       <c r="D70" s="2"/>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D71" s="2"/>
+      <c r="H71" s="9"/>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.45">
       <c r="H72" s="9"/>
     </row>
-    <row r="73" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="H73" s="9"/>
+    <row r="74" spans="4:8" x14ac:dyDescent="0.45">
+      <c r="H74" s="9"/>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.45">
       <c r="H75" s="9"/>
     </row>
-    <row r="76" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="H76" s="9"/>
+    <row r="78" spans="4:8" x14ac:dyDescent="0.45">
+      <c r="H78" s="9"/>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.45">
       <c r="H79" s="9"/>
@@ -3557,8 +3513,8 @@
     <row r="85" spans="8:8" x14ac:dyDescent="0.45">
       <c r="H85" s="9"/>
     </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H86" s="9"/>
+    <row r="89" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H89" s="9"/>
     </row>
     <row r="90" spans="8:8" x14ac:dyDescent="0.45">
       <c r="H90" s="9"/>
@@ -3566,14 +3522,11 @@
     <row r="91" spans="8:8" x14ac:dyDescent="0.45">
       <c r="H91" s="9"/>
     </row>
-    <row r="92" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H92" s="9"/>
-    </row>
-    <row r="94" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H94" s="9"/>
+    <row r="93" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H93" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T95" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T94" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
@@ -3583,19 +3536,19 @@
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D997</xm:sqref>
+          <xm:sqref>D2:D996</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J997</xm:sqref>
+          <xm:sqref>J2:J996</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I997</xm:sqref>
+          <xm:sqref>I2:I996</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/personalia/9 JR.xlsx
+++ b/data/personalia/9 JR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="332" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8575BD00-6E52-474B-8977-B56C74E4C6F1}"/>
+  <xr:revisionPtr revIDLastSave="338" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D61CD5E-7B07-48F7-96BA-C38DB504A519}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="188">
   <si>
     <t>Wilayah</t>
   </si>
@@ -587,6 +587,12 @@
   </si>
   <si>
     <t>PMP.031189.75600</t>
+  </si>
+  <si>
+    <t>RYAN ADI SAPUTRA</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL 9.6 Ktg</t>
   </si>
 </sst>
 </file>
@@ -3424,7 +3430,45 @@
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="D53" s="2"/>
+      <c r="A53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" s="2">
+        <v>77811</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H53" s="6">
+        <v>45809</v>
+      </c>
+      <c r="I53" s="2">
+        <v>4</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K53" s="6">
+        <v>45689</v>
+      </c>
+      <c r="L53" s="6">
+        <v>46084</v>
+      </c>
+      <c r="M53" s="6">
+        <v>20455</v>
+      </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.45">
       <c r="D54" s="2"/>

--- a/data/personalia/9 JR.xlsx
+++ b/data/personalia/9 JR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="338" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D61CD5E-7B07-48F7-96BA-C38DB504A519}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC67E975-6EFD-4BBB-8E7C-E8C54271CA40}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="192">
   <si>
     <t>Wilayah</t>
   </si>
@@ -593,6 +593,18 @@
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 9.6 Ktg</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
   </si>
 </sst>
 </file>
@@ -651,7 +663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -673,9 +685,6 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -982,7 +991,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T93"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:T94"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
@@ -998,10 +1008,10 @@
     <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
     <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
-    <col min="16" max="16" width="22" style="3" customWidth="1"/>
-    <col min="17" max="17" width="22" style="2" customWidth="1"/>
+    <col min="16" max="17" width="22" style="2" customWidth="1"/>
     <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="20" width="22" style="3" customWidth="1"/>
+    <col min="19" max="19" width="22" style="2" customWidth="1"/>
+    <col min="20" max="20" width="22" style="3" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
@@ -1067,7 +1077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
@@ -1113,12 +1123,14 @@
       <c r="O2" s="6">
         <v>46937</v>
       </c>
+      <c r="P2" s="3"/>
       <c r="Q2" s="2" t="s">
         <v>143</v>
       </c>
       <c r="R2" s="6">
         <v>46937</v>
       </c>
+      <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
@@ -1160,18 +1172,15 @@
       <c r="M3" s="6">
         <v>47727</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="O3" s="6">
-        <v>46448</v>
-      </c>
       <c r="Q3" s="2" t="s">
         <v>144</v>
       </c>
       <c r="R3" s="6">
         <v>46448</v>
       </c>
+      <c r="S3" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
@@ -1219,14 +1228,20 @@
       <c r="O4" s="6">
         <v>45696</v>
       </c>
+      <c r="P4" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="Q4" s="2" t="s">
         <v>182</v>
       </c>
       <c r="R4" s="6">
         <v>47370</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="S4" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
@@ -1272,8 +1287,10 @@
       <c r="O5" s="6">
         <v>46446</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P5" s="3"/>
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
@@ -1319,14 +1336,16 @@
       <c r="O6" s="6">
         <v>46837</v>
       </c>
+      <c r="P6" s="3"/>
       <c r="Q6" s="2" t="s">
         <v>183</v>
       </c>
       <c r="R6" s="6">
         <v>47114</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S6" s="3"/>
+    </row>
+    <row r="7" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>44</v>
       </c>
@@ -1372,8 +1391,12 @@
       <c r="O7" s="6">
         <v>46448</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>44</v>
       </c>
@@ -1419,8 +1442,12 @@
       <c r="O8" s="6">
         <v>46610</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="P8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>44</v>
       </c>
@@ -1461,7 +1488,7 @@
         <v>54544</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>44</v>
       </c>
@@ -1501,8 +1528,9 @@
       <c r="M10" s="6">
         <v>48245</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>44</v>
       </c>
@@ -1548,8 +1576,12 @@
       <c r="O11" s="6">
         <v>47324</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="P11" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -1595,8 +1627,11 @@
       <c r="O12" s="6">
         <v>46937</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P12" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>44</v>
       </c>
@@ -1642,8 +1677,12 @@
       <c r="O13" s="6">
         <v>47175</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P13" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -1689,8 +1728,12 @@
       <c r="O14" s="6">
         <v>46950</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="P14" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>44</v>
       </c>
@@ -1736,8 +1779,12 @@
       <c r="O15" s="6">
         <v>46950</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="P15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>44</v>
       </c>
@@ -1783,8 +1830,12 @@
       <c r="O16" s="6">
         <v>47114</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P16" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>44</v>
       </c>
@@ -1830,8 +1881,12 @@
       <c r="O17" s="6">
         <v>46433</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P17" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>44</v>
       </c>
@@ -1877,8 +1932,12 @@
       <c r="O18" s="6">
         <v>46433</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P18" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>44</v>
       </c>
@@ -1924,8 +1983,12 @@
       <c r="O19" s="6">
         <v>46916</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P19" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>44</v>
       </c>
@@ -1971,14 +2034,20 @@
       <c r="O20" s="6">
         <v>47175</v>
       </c>
+      <c r="P20" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="Q20" s="2" t="s">
         <v>184</v>
       </c>
       <c r="R20" s="6">
         <v>47370</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S20" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>44</v>
       </c>
@@ -2018,8 +2087,9 @@
       <c r="M21" s="6">
         <v>51622</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>44</v>
       </c>
@@ -2065,8 +2135,12 @@
       <c r="O22" s="6">
         <v>46881</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P22" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
@@ -2112,8 +2186,12 @@
       <c r="O23" s="6">
         <v>46433</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
@@ -2159,8 +2237,12 @@
       <c r="O24" s="6">
         <v>46433</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P24" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
         <v>44</v>
       </c>
@@ -2200,8 +2282,9 @@
       <c r="M25" s="6">
         <v>20455</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>44</v>
       </c>
@@ -2247,9 +2330,12 @@
       <c r="O26" s="6">
         <v>46610</v>
       </c>
-      <c r="P26" s="8"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
@@ -2295,8 +2381,11 @@
       <c r="O27" s="6">
         <v>47203</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P27" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -2342,8 +2431,12 @@
       <c r="O28" s="6">
         <v>47175</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>44</v>
       </c>
@@ -2389,8 +2482,12 @@
       <c r="O29" s="6">
         <v>47203</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P29" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
@@ -2430,8 +2527,9 @@
       <c r="M30" s="6">
         <v>20455</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
         <v>44</v>
       </c>
@@ -2471,8 +2569,9 @@
       <c r="M31" s="6">
         <v>20455</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>44</v>
       </c>
@@ -2512,8 +2611,9 @@
       <c r="M32" s="6">
         <v>55885</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>44</v>
       </c>
@@ -2559,8 +2659,12 @@
       <c r="O33" s="6">
         <v>47265</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P33" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
@@ -2606,8 +2710,12 @@
       <c r="O34" s="6">
         <v>46446</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P34" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>44</v>
       </c>
@@ -2648,7 +2756,7 @@
         <v>46997</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2796,9 @@
       <c r="M36" s="6">
         <v>54455</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S36" s="3"/>
+    </row>
+    <row r="37" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>44</v>
       </c>
@@ -2735,8 +2844,12 @@
       <c r="O37" s="6">
         <v>46446</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P37" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S37" s="3"/>
+    </row>
+    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
         <v>44</v>
       </c>
@@ -2782,8 +2895,12 @@
       <c r="O38" s="6">
         <v>47175</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P38" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S38" s="3"/>
+    </row>
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
         <v>44</v>
       </c>
@@ -2829,8 +2946,12 @@
       <c r="O39" s="6">
         <v>46476</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P39" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
         <v>44</v>
       </c>
@@ -2876,8 +2997,12 @@
       <c r="O40" s="6">
         <v>46433</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P40" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
         <v>44</v>
       </c>
@@ -2923,8 +3048,11 @@
       <c r="O41" s="6">
         <v>47114</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P41" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
         <v>44</v>
       </c>
@@ -2970,8 +3098,12 @@
       <c r="O42" s="6">
         <v>47324</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P42" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
         <v>44</v>
       </c>
@@ -3017,8 +3149,12 @@
       <c r="O43" s="6">
         <v>47114</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P43" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>44</v>
       </c>
@@ -3058,8 +3194,9 @@
       <c r="M44" s="6">
         <v>20455</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
@@ -3099,8 +3236,9 @@
       <c r="M45" s="6">
         <v>20455</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
         <v>44</v>
       </c>
@@ -3146,8 +3284,12 @@
       <c r="O46" s="6">
         <v>46433</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P46" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
         <v>44</v>
       </c>
@@ -3193,14 +3335,20 @@
       <c r="O47" s="6">
         <v>47114</v>
       </c>
+      <c r="P47" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="Q47" s="2" t="s">
         <v>185</v>
       </c>
       <c r="R47" s="6">
         <v>47370</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S47" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>44</v>
       </c>
@@ -3240,8 +3388,9 @@
       <c r="M48" s="6">
         <v>52994</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="1:18" s="3" customFormat="1" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3436,13 @@
       <c r="O49" s="6">
         <v>47324</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P49" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="6"/>
+    </row>
+    <row r="50" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
         <v>44</v>
       </c>
@@ -3334,8 +3488,13 @@
       <c r="O50" s="6">
         <v>46837</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P50" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="6"/>
+    </row>
+    <row r="51" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
         <v>44</v>
       </c>
@@ -3381,8 +3540,13 @@
       <c r="O51" s="6">
         <v>46433</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P51" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="6"/>
+    </row>
+    <row r="52" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>44</v>
       </c>
@@ -3428,8 +3592,13 @@
       <c r="O52" s="6">
         <v>47114</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P52" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="6"/>
+    </row>
+    <row r="53" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
         <v>44</v>
       </c>
@@ -3469,113 +3638,739 @@
       <c r="M53" s="6">
         <v>20455</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="N53" s="2"/>
+      <c r="O53" s="6"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="6"/>
+    </row>
+    <row r="54" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="2"/>
+      <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="E54" s="2"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="6"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="6"/>
+    </row>
+    <row r="55" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="2"/>
+      <c r="C55" s="2"/>
       <c r="D55" s="2"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="E55" s="2"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="6"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="6"/>
+    </row>
+    <row r="56" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="2"/>
+      <c r="C56" s="2"/>
       <c r="D56" s="2"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="E56" s="2"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="6"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="6"/>
+    </row>
+    <row r="57" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="2"/>
+      <c r="C57" s="2"/>
       <c r="D57" s="2"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="E57" s="2"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="6"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="6"/>
+    </row>
+    <row r="58" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="2"/>
+      <c r="C58" s="2"/>
       <c r="D58" s="2"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="E58" s="2"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="6"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="6"/>
+    </row>
+    <row r="59" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="2"/>
+      <c r="C59" s="2"/>
       <c r="D59" s="2"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="E59" s="2"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="6"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="6"/>
+    </row>
+    <row r="60" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="2"/>
+      <c r="C60" s="2"/>
       <c r="D60" s="2"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="E60" s="2"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="6"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="6"/>
+    </row>
+    <row r="61" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="2"/>
+      <c r="C61" s="2"/>
       <c r="D61" s="2"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="E61" s="2"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="6"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="6"/>
+    </row>
+    <row r="62" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="2"/>
+      <c r="C62" s="2"/>
       <c r="D62" s="2"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="E62" s="2"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="6"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="6"/>
+    </row>
+    <row r="63" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="2"/>
+      <c r="C63" s="2"/>
       <c r="D63" s="2"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="E63" s="2"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="6"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="6"/>
+    </row>
+    <row r="64" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="2"/>
+      <c r="C64" s="2"/>
       <c r="D64" s="2"/>
-    </row>
-    <row r="65" spans="4:8" x14ac:dyDescent="0.45">
+      <c r="E64" s="2"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="6"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="6"/>
+    </row>
+    <row r="65" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="2"/>
+      <c r="C65" s="2"/>
       <c r="D65" s="2"/>
-    </row>
-    <row r="66" spans="4:8" x14ac:dyDescent="0.45">
+      <c r="E65" s="2"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="6"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="6"/>
+    </row>
+    <row r="66" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="2"/>
+      <c r="C66" s="2"/>
       <c r="D66" s="2"/>
-    </row>
-    <row r="67" spans="4:8" x14ac:dyDescent="0.45">
+      <c r="E66" s="2"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="6"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="6"/>
+    </row>
+    <row r="67" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="2"/>
+      <c r="C67" s="2"/>
       <c r="D67" s="2"/>
-    </row>
-    <row r="68" spans="4:8" x14ac:dyDescent="0.45">
+      <c r="E67" s="2"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="6"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="6"/>
+    </row>
+    <row r="68" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="2"/>
+      <c r="C68" s="2"/>
       <c r="D68" s="2"/>
-    </row>
-    <row r="69" spans="4:8" x14ac:dyDescent="0.45">
+      <c r="E68" s="2"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="6"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="6"/>
+    </row>
+    <row r="69" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="2"/>
+      <c r="C69" s="2"/>
       <c r="D69" s="2"/>
-    </row>
-    <row r="70" spans="4:8" x14ac:dyDescent="0.45">
+      <c r="E69" s="2"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="6"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="6"/>
+    </row>
+    <row r="70" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="2"/>
+      <c r="C70" s="2"/>
       <c r="D70" s="2"/>
-    </row>
-    <row r="71" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="H71" s="9"/>
-    </row>
-    <row r="72" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="H72" s="9"/>
-    </row>
-    <row r="74" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="H74" s="9"/>
-    </row>
-    <row r="75" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="H75" s="9"/>
-    </row>
-    <row r="78" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="H78" s="9"/>
-    </row>
-    <row r="79" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="H79" s="9"/>
-    </row>
-    <row r="80" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="H80" s="9"/>
-    </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H81" s="9"/>
-    </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H82" s="9"/>
-    </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H83" s="9"/>
-    </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H84" s="9"/>
-    </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H85" s="9"/>
-    </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H89" s="9"/>
-    </row>
-    <row r="90" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H90" s="9"/>
-    </row>
-    <row r="91" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H91" s="9"/>
-    </row>
-    <row r="93" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H93" s="9"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="6"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="6"/>
+    </row>
+    <row r="71" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="6"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="6"/>
+    </row>
+    <row r="72" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="6"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="6"/>
+    </row>
+    <row r="73" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="6"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="6"/>
+    </row>
+    <row r="74" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="6"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="6"/>
+    </row>
+    <row r="75" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="6"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="6"/>
+    </row>
+    <row r="76" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="6"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="6"/>
+    </row>
+    <row r="77" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="6"/>
+      <c r="Q77" s="2"/>
+      <c r="R77" s="6"/>
+    </row>
+    <row r="78" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="6"/>
+      <c r="Q78" s="2"/>
+      <c r="R78" s="6"/>
+    </row>
+    <row r="79" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="2"/>
+      <c r="O79" s="6"/>
+      <c r="Q79" s="2"/>
+      <c r="R79" s="6"/>
+    </row>
+    <row r="80" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="2"/>
+      <c r="O80" s="6"/>
+      <c r="Q80" s="2"/>
+      <c r="R80" s="6"/>
+    </row>
+    <row r="81" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="2"/>
+      <c r="O81" s="6"/>
+      <c r="Q81" s="2"/>
+      <c r="R81" s="6"/>
+    </row>
+    <row r="82" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
+      <c r="N82" s="2"/>
+      <c r="O82" s="6"/>
+      <c r="Q82" s="2"/>
+      <c r="R82" s="6"/>
+    </row>
+    <row r="83" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="2"/>
+      <c r="O83" s="6"/>
+      <c r="Q83" s="2"/>
+      <c r="R83" s="6"/>
+    </row>
+    <row r="84" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="2"/>
+      <c r="O84" s="6"/>
+      <c r="Q84" s="2"/>
+      <c r="R84" s="6"/>
+    </row>
+    <row r="85" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="6"/>
+      <c r="Q85" s="2"/>
+      <c r="R85" s="6"/>
+    </row>
+    <row r="86" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="2"/>
+      <c r="O86" s="6"/>
+      <c r="Q86" s="2"/>
+      <c r="R86" s="6"/>
+    </row>
+    <row r="87" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="6"/>
+      <c r="N87" s="2"/>
+      <c r="O87" s="6"/>
+      <c r="Q87" s="2"/>
+      <c r="R87" s="6"/>
+    </row>
+    <row r="88" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="6"/>
+      <c r="N88" s="2"/>
+      <c r="O88" s="6"/>
+      <c r="Q88" s="2"/>
+      <c r="R88" s="6"/>
+    </row>
+    <row r="89" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="6"/>
+      <c r="N89" s="2"/>
+      <c r="O89" s="6"/>
+      <c r="Q89" s="2"/>
+      <c r="R89" s="6"/>
+    </row>
+    <row r="90" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="6"/>
+      <c r="N90" s="2"/>
+      <c r="O90" s="6"/>
+      <c r="Q90" s="2"/>
+      <c r="R90" s="6"/>
+    </row>
+    <row r="91" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="2"/>
+      <c r="O91" s="6"/>
+      <c r="Q91" s="2"/>
+      <c r="R91" s="6"/>
+    </row>
+    <row r="92" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="6"/>
+      <c r="N92" s="2"/>
+      <c r="O92" s="6"/>
+      <c r="Q92" s="2"/>
+      <c r="R92" s="6"/>
+    </row>
+    <row r="93" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
+      <c r="N93" s="2"/>
+      <c r="O93" s="6"/>
+      <c r="Q93" s="2"/>
+      <c r="R93" s="6"/>
+    </row>
+    <row r="94" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="2"/>
+      <c r="O94" s="6"/>
+      <c r="Q94" s="2"/>
+      <c r="R94" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T94" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T94" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="QC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>

--- a/data/personalia/9 JR.xlsx
+++ b/data/personalia/9 JR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="380" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC67E975-6EFD-4BBB-8E7C-E8C54271CA40}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5422CED8-D749-49EA-B004-BCE7DB09EAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,19 @@
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$199</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="227">
   <si>
     <t>Wilayah</t>
   </si>
@@ -163,448 +172,553 @@
     <t>Kaur UPT Workshop</t>
   </si>
   <si>
+    <t>WS LAA Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.4 Thb</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>LAA 1.1 Rk</t>
+  </si>
+  <si>
+    <t>LAA 1.14 Nmo</t>
+  </si>
+  <si>
+    <t>LAA 1.2 Prp</t>
+  </si>
+  <si>
+    <t>LAA 1.3 Srp</t>
+  </si>
+  <si>
+    <t>LAA 1.5 Du</t>
+  </si>
+  <si>
+    <t>LAA 1.11 Psm</t>
+  </si>
+  <si>
+    <t>LAA 1.6 Jakk</t>
+  </si>
+  <si>
+    <t>LAA 1.7 Pse</t>
+  </si>
+  <si>
+    <t>LAA 1.8 Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.9 Jng</t>
+  </si>
+  <si>
+    <t>LAA 1.10 Ckr</t>
+  </si>
+  <si>
+    <t>LAA 1.12 Dp</t>
+  </si>
+  <si>
+    <t>LAA 1.13 Boo</t>
+  </si>
+  <si>
+    <t>LAA 1.15 Bst</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>Calon Pekerja</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana</t>
+  </si>
+  <si>
+    <t>Calon Teknisi</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Calon Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Kepala UPT BYST</t>
+  </si>
+  <si>
+    <t>Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 2</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 2</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop And OCC Signalling and Communication</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop Power System And OCC Power</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
+    <t>Supervisor Perbaikan UPT Workshop Sintelis</t>
+  </si>
+  <si>
+    <t>Supervisor Rekayasa Perawatan UPT Workshop Sintelis</t>
+  </si>
+  <si>
     <t>9 JR</t>
   </si>
   <si>
     <t>AGUNG NUGROHO DWI ATMOJO</t>
   </si>
   <si>
+    <t>Manager STL Daop 9 Jr</t>
+  </si>
+  <si>
+    <t>PMP.231078.00910</t>
+  </si>
+  <si>
     <t>ANTON ADI LAKSONO</t>
   </si>
   <si>
+    <t>PLT QC STL 9A Jr</t>
+  </si>
+  <si>
+    <t>PMP.050874.41240</t>
+  </si>
+  <si>
     <t>JUNIANTO</t>
   </si>
   <si>
+    <t>QC STL 9B Bw</t>
+  </si>
+  <si>
+    <t>PMP.050671.74674</t>
+  </si>
+  <si>
     <t>YESSY CARMAYLINNA</t>
   </si>
   <si>
+    <t>AM Fasilitas Daop 9 Jr</t>
+  </si>
+  <si>
+    <t>PRP.260592.39443</t>
+  </si>
+  <si>
     <t>MUHAMMAD SIFA' HIDAYAT</t>
   </si>
   <si>
+    <t>AM Program Sintelis dan Rekayasa Teknik Daop 9 Jr</t>
+  </si>
+  <si>
+    <t>PRP.011287.00572</t>
+  </si>
+  <si>
+    <t>PMP.011287.122370</t>
+  </si>
+  <si>
     <t>HENNY SUTRIYAWATI</t>
   </si>
   <si>
+    <t>Pelaksana Program Sintelis dan Rekayasa Teknis</t>
+  </si>
+  <si>
+    <t>PRP.231092.41078</t>
+  </si>
+  <si>
     <t>YUSUF HARIYADI</t>
   </si>
   <si>
+    <t>PRP.050492.00580</t>
+  </si>
+  <si>
     <t>WAWAN MAULANA SULTON</t>
   </si>
   <si>
+    <t>Kepala UPT Workshop STL Jr</t>
+  </si>
+  <si>
+    <t>WS Jr</t>
+  </si>
+  <si>
     <t>EKO ABDUL SOLEH</t>
   </si>
   <si>
+    <t>9.1 Pb</t>
+  </si>
+  <si>
+    <t>PRP.200176.126900</t>
+  </si>
+  <si>
     <t>MULYANA</t>
   </si>
   <si>
+    <t>PRP.230470.126895</t>
+  </si>
+  <si>
     <t>IWAN SAFTRIAWAN</t>
   </si>
   <si>
+    <t>Kepala UPT Resor Kelas C 9.1 Pb</t>
+  </si>
+  <si>
+    <t>PRP.271087.123427</t>
+  </si>
+  <si>
     <t>BAYU EKO PUTRO</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.1 Pb</t>
+  </si>
+  <si>
+    <t>PRP.121286.127123</t>
+  </si>
+  <si>
     <t>ABU JIANTO</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.1 Pb</t>
+  </si>
+  <si>
+    <t>PRP.250291.00667</t>
+  </si>
+  <si>
     <t>VIDI LOKANANTA JULIO</t>
   </si>
   <si>
+    <t>PNC Perbaikan UPT Resor STL 9.1 Pb</t>
+  </si>
+  <si>
+    <t>PRP.280795.122308</t>
+  </si>
+  <si>
     <t>RONDIK PRASTIYA</t>
   </si>
   <si>
+    <t>PRP.280588.126560</t>
+  </si>
+  <si>
     <t>ZAINAL ARIFIN</t>
   </si>
   <si>
+    <t>PNC Preventif UPT Resor STL 9.1 Pb</t>
+  </si>
+  <si>
+    <t>PRP.221296.40697</t>
+  </si>
+  <si>
     <t>AHMAD AINUR RIDHO</t>
   </si>
   <si>
+    <t>PRP.310196.40567</t>
+  </si>
+  <si>
     <t>WIDIHARJO MUSTIKANE DEWOTO</t>
   </si>
   <si>
+    <t>PRP.240801.57674</t>
+  </si>
+  <si>
     <t>SLAMET NURBAHTIYAR</t>
   </si>
   <si>
+    <t>Kepala UPT Resor Kelas C 9.2 Kk</t>
+  </si>
+  <si>
+    <t>9.2 Kk</t>
+  </si>
+  <si>
+    <t>PRP.231285.126569</t>
+  </si>
+  <si>
+    <t>PMP.231285.75601</t>
+  </si>
+  <si>
     <t>ROIMARTIN</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.2 Kk</t>
+  </si>
+  <si>
+    <t>PRP.230485.00615</t>
+  </si>
+  <si>
     <t>MUHAMMAD DZULKARNAIN</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.2 Kk</t>
+  </si>
+  <si>
+    <t>PRP.031192.00630</t>
+  </si>
+  <si>
     <t>BAGUS CAHYA PAMUNGKAS</t>
   </si>
   <si>
+    <t>PNC Perbaikan UPT Resor STL 9.2 Kk</t>
+  </si>
+  <si>
+    <t>PRP.071194.40423</t>
+  </si>
+  <si>
     <t>WASKITO ENDRO LESMONO</t>
   </si>
   <si>
+    <t>PRP.280194.40425</t>
+  </si>
+  <si>
     <t>SHONUFIT AR ROYAN FIRDAUS</t>
   </si>
   <si>
+    <t>PNC Preventif UPT Resor STL 9.2 Kk</t>
+  </si>
+  <si>
     <t>PUJIONO</t>
   </si>
   <si>
+    <t>PRP.091279.00641</t>
+  </si>
+  <si>
     <t>DJOKO RUSTANTO</t>
   </si>
   <si>
+    <t>Kepala UPT Resor Kelas C 9.3 Jr</t>
+  </si>
+  <si>
+    <t>9.3 Jr</t>
+  </si>
+  <si>
+    <t>PRP.091276.126620</t>
+  </si>
+  <si>
     <t>HARIS ANGGRIAWAN</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.3 Jr</t>
+  </si>
+  <si>
+    <t>PRP.090693.126823</t>
+  </si>
+  <si>
     <t>DIDIN DWI PRATONO</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.3 Jr</t>
+  </si>
+  <si>
+    <t>PRP.141287.126822</t>
+  </si>
+  <si>
     <t>RIZKY WAHYU PRATAMA</t>
   </si>
   <si>
+    <t>PNC Perbaikan UPT Resor STL 9.3 Jr</t>
+  </si>
+  <si>
     <t>AHMAD SYAIFUL ZAKARIA</t>
   </si>
   <si>
     <t>AHMAD ZAHRONI</t>
   </si>
   <si>
+    <t>PRP.301296.40905</t>
+  </si>
+  <si>
     <t>IRWIEN CAHYONO</t>
   </si>
   <si>
+    <t>PRP.160181.00640</t>
+  </si>
+  <si>
     <t>AHMAD BASTOMY</t>
   </si>
   <si>
+    <t>PNC Preventif UPT Resor STL 9.3 Jr</t>
+  </si>
+  <si>
+    <t>PRP.030298.39722</t>
+  </si>
+  <si>
     <t>HERI PURWANTO</t>
   </si>
   <si>
+    <t>Kepala UPT Resor Kelas C 9.4 Klt</t>
+  </si>
+  <si>
+    <t>9.4 Klt</t>
+  </si>
+  <si>
+    <t>PRP.050872.127184</t>
+  </si>
+  <si>
     <t>YAZID MIFTAHUL HUDA</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.4 Klt</t>
+  </si>
+  <si>
+    <t>PRP.280193.00672</t>
+  </si>
+  <si>
     <t>SONI FERDIYANSYAH</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.4 Klt</t>
+  </si>
+  <si>
+    <t>PRP.061196.39723</t>
+  </si>
+  <si>
     <t>EDI SUDARSO</t>
   </si>
   <si>
+    <t>PNC Perbaikan UPT Resor STL 9.4 Klt</t>
+  </si>
+  <si>
+    <t>PRP.160673.00583</t>
+  </si>
+  <si>
     <t>HARUN ARROSYID</t>
   </si>
   <si>
+    <t>PRP.190497.41652</t>
+  </si>
+  <si>
     <t>FENGKY SEPTIAN ADI PUTRA</t>
   </si>
   <si>
+    <t>PNC Preventif UPT Resor STL 9.4 Klt</t>
+  </si>
+  <si>
+    <t>PRP.160991.40424</t>
+  </si>
+  <si>
     <t>HENDRA GUNAWAN</t>
   </si>
   <si>
+    <t>Kepala UPT Resor Kelas C 9.5 Kbr</t>
+  </si>
+  <si>
+    <t>9.5 Kbr</t>
+  </si>
+  <si>
+    <t>PRP.051189.126553</t>
+  </si>
+  <si>
     <t>BAGUS PUJIANTO</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.5 Kbr</t>
+  </si>
+  <si>
+    <t>PRP.090892.00643</t>
+  </si>
+  <si>
     <t>DODY PRASETYONO</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.5 Kbr</t>
+  </si>
+  <si>
+    <t>PRP.070693.00579</t>
+  </si>
+  <si>
     <t>AGIL WIBOWO</t>
   </si>
   <si>
+    <t>PNC Perbaikan UPT Resor STL 9.5 Kbr</t>
+  </si>
+  <si>
     <t>FARZYDAN OKTA VIANDRA DWI PUTRA</t>
   </si>
   <si>
     <t>RAIHAN WABRIANSYAH RAMADHAN</t>
   </si>
   <si>
+    <t>PNC Preventif UPT Resor STL 9.5 Kbr</t>
+  </si>
+  <si>
+    <t>PRP.290197.40696</t>
+  </si>
+  <si>
     <t>ARIEF IKHSAN</t>
   </si>
   <si>
+    <t>Kepala UPT Resor Kelas C 9.6 Ktg</t>
+  </si>
+  <si>
+    <t>9.6 Ktg</t>
+  </si>
+  <si>
+    <t>PRP.031189.126428</t>
+  </si>
+  <si>
+    <t>PMP.031189.75600</t>
+  </si>
+  <si>
     <t>ROSULI ERWAN</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.6 Ktg</t>
+  </si>
+  <si>
+    <t>PRP.040189.128718</t>
+  </si>
+  <si>
     <t>RUSTAM EFENDI</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.6 Ktg</t>
+  </si>
+  <si>
+    <t>PRP.050689.126568</t>
+  </si>
+  <si>
     <t>FARID INDRA SUKMA</t>
   </si>
   <si>
+    <t>PNC Perbaikan UPT Resor STL 9.6 Ktg</t>
+  </si>
+  <si>
+    <t>PRP.281092.117995</t>
+  </si>
+  <si>
     <t>FERDIANSYAH</t>
   </si>
   <si>
+    <t>PRP.170298.40390</t>
+  </si>
+  <si>
     <t>SUJANARKO</t>
   </si>
   <si>
-    <t>Calon Pekerja</t>
-  </si>
-  <si>
-    <t>Calon Petugas Negative Check</t>
-  </si>
-  <si>
-    <t>Manager STL Daop 9 Jr</t>
-  </si>
-  <si>
-    <t>PLT QC STL 9A Jr</t>
-  </si>
-  <si>
-    <t>QC STL 9B Bw</t>
-  </si>
-  <si>
-    <t>AM Fasilitas Daop 9 Jr</t>
-  </si>
-  <si>
-    <t>AM Program Sintelis dan Rekayasa Teknik Daop 9 Jr</t>
-  </si>
-  <si>
-    <t>Pelaksana Program Sintelis dan Rekayasa Teknis</t>
-  </si>
-  <si>
-    <t>Kepala UPT Workshop STL Jr</t>
-  </si>
-  <si>
-    <t>WS Jr</t>
-  </si>
-  <si>
-    <t>Supervisor Perbaikan UPT Workshop Sintelis</t>
-  </si>
-  <si>
-    <t>9.1 Pb</t>
-  </si>
-  <si>
-    <t>Supervisor Rekayasa Perawatan UPT Workshop Sintelis</t>
-  </si>
-  <si>
-    <t>Kepala UPT Resor Kelas C 9.1 Pb</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.1 Pb</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.1 Pb</t>
-  </si>
-  <si>
-    <t>PNC Perbaikan UPT Resor STL 9.1 Pb</t>
-  </si>
-  <si>
-    <t>PNC Preventif UPT Resor STL 9.1 Pb</t>
-  </si>
-  <si>
-    <t>Kepala UPT Resor Kelas C 9.2 Kk</t>
-  </si>
-  <si>
-    <t>9.2 Kk</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.2 Kk</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.2 Kk</t>
-  </si>
-  <si>
-    <t>PNC Perbaikan UPT Resor STL 9.2 Kk</t>
-  </si>
-  <si>
-    <t>PNC Preventif UPT Resor STL 9.2 Kk</t>
-  </si>
-  <si>
-    <t>Kepala UPT Resor Kelas C 9.3 Jr</t>
-  </si>
-  <si>
-    <t>9.3 Jr</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.3 Jr</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.3 Jr</t>
-  </si>
-  <si>
-    <t>PNC Perbaikan UPT Resor STL 9.3 Jr</t>
-  </si>
-  <si>
-    <t>PNC Preventif UPT Resor STL 9.3 Jr</t>
-  </si>
-  <si>
-    <t>Kepala UPT Resor Kelas C 9.4 Klt</t>
-  </si>
-  <si>
-    <t>9.4 Klt</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.4 Klt</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.4 Klt</t>
-  </si>
-  <si>
-    <t>PNC Perbaikan UPT Resor STL 9.4 Klt</t>
-  </si>
-  <si>
-    <t>PNC Preventif UPT Resor STL 9.4 Klt</t>
-  </si>
-  <si>
-    <t>Kepala UPT Resor Kelas C 9.5 Kbr</t>
-  </si>
-  <si>
-    <t>9.5 Kbr</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.5 Kbr</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.5 Kbr</t>
-  </si>
-  <si>
-    <t>PNC Perbaikan UPT Resor STL 9.5 Kbr</t>
-  </si>
-  <si>
-    <t>PNC Preventif UPT Resor STL 9.5 Kbr</t>
-  </si>
-  <si>
-    <t>Kepala UPT Resor Kelas C 9.6 Ktg</t>
-  </si>
-  <si>
-    <t>9.6 Ktg</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 9.6 Ktg</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 9.6 Ktg</t>
-  </si>
-  <si>
-    <t>PNC Perbaikan UPT Resor STL 9.6 Ktg</t>
-  </si>
-  <si>
-    <t>PMP.231078.00910</t>
-  </si>
-  <si>
-    <t>PMP.050874.41240</t>
-  </si>
-  <si>
-    <t>PRP. 050671. 127183</t>
-  </si>
-  <si>
-    <t>PRP.260592.39443</t>
-  </si>
-  <si>
-    <t>PRP.011287.00572</t>
-  </si>
-  <si>
-    <t>PRP.231092.41078</t>
-  </si>
-  <si>
-    <t>PRP.050492.00580</t>
-  </si>
-  <si>
-    <t>PRP.230470.126895</t>
-  </si>
-  <si>
-    <t>PRP.271087.123427</t>
-  </si>
-  <si>
-    <t>PRP.121286.127123</t>
-  </si>
-  <si>
-    <t>PRP.250291.00667</t>
-  </si>
-  <si>
-    <t>PRP.280795.122308</t>
-  </si>
-  <si>
-    <t>PRP.280588.126560</t>
-  </si>
-  <si>
-    <t>PRP.221296.40697</t>
-  </si>
-  <si>
-    <t>PRP.310196.40567</t>
-  </si>
-  <si>
-    <t>PRP.240801.57674</t>
-  </si>
-  <si>
-    <t>PRP.231285.126569</t>
-  </si>
-  <si>
-    <t>PRP.031192.00630</t>
-  </si>
-  <si>
-    <t>PRP.071194.40423</t>
-  </si>
-  <si>
-    <t>PRP.280194.40425</t>
-  </si>
-  <si>
-    <t>PRP.091279.00641</t>
-  </si>
-  <si>
-    <t>PRP.091276.126620</t>
-  </si>
-  <si>
-    <t>PRP.090693.126823</t>
-  </si>
-  <si>
-    <t>PRP.141287.126822</t>
-  </si>
-  <si>
-    <t>PRP.160181.00640</t>
-  </si>
-  <si>
-    <t>PRP.030298.39722</t>
-  </si>
-  <si>
-    <t>PRP.061196.39723</t>
-  </si>
-  <si>
-    <t>PRP.160673.00583</t>
-  </si>
-  <si>
-    <t>PRP.190497.41652</t>
-  </si>
-  <si>
-    <t>PRP.160991.40424</t>
-  </si>
-  <si>
-    <t>PRP.051189.126553</t>
-  </si>
-  <si>
-    <t>PRP.090892.00643</t>
-  </si>
-  <si>
-    <t>PRP.070693.00579</t>
-  </si>
-  <si>
-    <t>PRP.290197.40696</t>
-  </si>
-  <si>
-    <t>PRP.031189.126428</t>
-  </si>
-  <si>
-    <t>PRP.050689.126568</t>
-  </si>
-  <si>
-    <t>PRP.281092.117995</t>
-  </si>
-  <si>
-    <t>PRP.170298.40390</t>
-  </si>
-  <si>
     <t>PRP.171087.00581</t>
   </si>
   <si>
-    <t>PMP.050671.74674</t>
-  </si>
-  <si>
-    <t>PMP.011287.122370</t>
-  </si>
-  <si>
-    <t>PMP.231285.75601</t>
-  </si>
-  <si>
-    <t>PMP.031189.75600</t>
-  </si>
-  <si>
     <t>RYAN ADI SAPUTRA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 9.6 Ktg</t>
-  </si>
-  <si>
-    <t>PRP Pelaksana</t>
-  </si>
-  <si>
-    <t>PRP Lanjutan</t>
-  </si>
-  <si>
-    <t>PMP Pelaksana</t>
-  </si>
-  <si>
-    <t>PMP Lanjutan</t>
   </si>
 </sst>
 </file>
@@ -675,9 +789,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -686,8 +797,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -991,31 +1105,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:T94"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.265625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.86328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.53125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
-    <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
+    <col min="11" max="13" width="13.1328125" style="5" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.1328125" style="5" customWidth="1"/>
     <col min="16" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="19" width="22" style="2" customWidth="1"/>
-    <col min="20" max="20" width="22" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.1328125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="22" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1037,7 +1149,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1046,19 +1158,19 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1067,7 +1179,7 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -1077,12 +1189,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2">
         <v>45918</v>
@@ -1093,13 +1205,13 @@
       <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>98</v>
+      <c r="F2" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>45903</v>
       </c>
       <c r="I2" s="2">
@@ -1108,36 +1220,31 @@
       <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>35490</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>28786</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="5">
         <v>49249</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="O2" s="6">
+      <c r="Q2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" s="5">
         <v>46937</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="R2" s="6">
-        <v>46937</v>
-      </c>
-      <c r="S2" s="3"/>
+      <c r="S2" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2">
         <v>42110</v>
@@ -1148,13 +1255,13 @@
       <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>99</v>
+      <c r="F3" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>45901</v>
       </c>
       <c r="I3" s="2">
@@ -1163,31 +1270,31 @@
       <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6">
-        <v>34346</v>
-      </c>
-      <c r="L3" s="6">
+      <c r="K3" s="5">
+        <v>34669</v>
+      </c>
+      <c r="L3" s="5">
         <v>27246</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="5">
         <v>47727</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="R3" s="6">
+        <v>88</v>
+      </c>
+      <c r="R3" s="5">
         <v>46448</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>191</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2">
         <v>42080</v>
@@ -1198,13 +1305,13 @@
       <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>100</v>
+      <c r="F4" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>45901</v>
       </c>
       <c r="I4" s="2">
@@ -1213,40 +1320,31 @@
       <c r="J4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>34669</v>
       </c>
-      <c r="L4" s="6">
-        <v>26089</v>
-      </c>
-      <c r="M4" s="6">
+      <c r="L4" s="5">
+        <v>27809</v>
+      </c>
+      <c r="M4" s="5">
         <v>46569</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="O4" s="6">
-        <v>45696</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="Q4" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="R4" s="6">
+        <v>91</v>
+      </c>
+      <c r="R4" s="5">
         <v>47370</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="C5" s="2">
         <v>67901</v>
@@ -1257,13 +1355,13 @@
       <c r="E5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>101</v>
+      <c r="F5" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>45945</v>
       </c>
       <c r="I5" s="2">
@@ -1272,30 +1370,31 @@
       <c r="J5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>42328</v>
       </c>
-      <c r="L5" s="6">
-        <v>33750</v>
-      </c>
-      <c r="M5" s="6">
+      <c r="L5" s="5">
+        <v>27304</v>
+      </c>
+      <c r="M5" s="5">
         <v>54210</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="O5" s="6">
+        <v>94</v>
+      </c>
+      <c r="O5" s="5">
         <v>46446</v>
       </c>
-      <c r="P5" s="3"/>
-      <c r="S5" s="3"/>
-    </row>
-    <row r="6" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+      <c r="P5" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C6" s="2">
         <v>50227</v>
@@ -1306,13 +1405,13 @@
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>102</v>
+      <c r="F6" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>45383</v>
       </c>
       <c r="I6" s="2">
@@ -1321,36 +1420,37 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L6" s="6">
-        <v>31789</v>
-      </c>
-      <c r="M6" s="6">
-        <v>52263</v>
+      <c r="K6" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L6" s="5">
+        <v>32112</v>
+      </c>
+      <c r="M6" s="5">
+        <v>52597</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="O6" s="6">
+        <v>97</v>
+      </c>
+      <c r="O6" s="5">
         <v>46837</v>
       </c>
-      <c r="P6" s="3"/>
+      <c r="P6" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q6" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="R6" s="6">
+        <v>98</v>
+      </c>
+      <c r="R6" s="5">
         <v>47114</v>
       </c>
-      <c r="S6" s="3"/>
-    </row>
-    <row r="7" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2">
         <v>69353</v>
@@ -1361,14 +1461,14 @@
       <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>103</v>
+      <c r="F7" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="6">
-        <v>44927</v>
+      <c r="H7" s="5">
+        <v>42767</v>
       </c>
       <c r="I7" s="2">
         <v>4</v>
@@ -1376,32 +1476,31 @@
       <c r="J7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="K7" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L7" s="5">
         <v>33900</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>54363</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O7" s="6">
+        <v>101</v>
+      </c>
+      <c r="O7" s="5">
         <v>46448</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S7" s="3"/>
-    </row>
-    <row r="8" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>61490</v>
@@ -1412,14 +1511,14 @@
       <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>103</v>
+      <c r="F8" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="6">
-        <v>44927</v>
+      <c r="H8" s="5">
+        <v>42010</v>
       </c>
       <c r="I8" s="2">
         <v>4</v>
@@ -1427,32 +1526,31 @@
       <c r="J8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L8" s="6">
-        <v>33728</v>
-      </c>
-      <c r="M8" s="6">
-        <v>54210</v>
+      <c r="K8" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L8" s="5">
+        <v>33699</v>
+      </c>
+      <c r="M8" s="5">
+        <v>54179</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="O8" s="6">
+        <v>103</v>
+      </c>
+      <c r="O8" s="5">
         <v>46610</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S8" s="3"/>
-    </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2">
         <v>61508</v>
@@ -1463,13 +1561,13 @@
       <c r="E9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>104</v>
+      <c r="F9" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H9" s="6">
+        <v>106</v>
+      </c>
+      <c r="H9" s="5">
         <v>45597</v>
       </c>
       <c r="I9" s="2">
@@ -1478,22 +1576,22 @@
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>40787</v>
       </c>
-      <c r="L9" s="6">
-        <v>34089</v>
-      </c>
-      <c r="M9" s="6">
+      <c r="L9" s="5">
+        <v>34060</v>
+      </c>
+      <c r="M9" s="5">
         <v>54544</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2">
         <v>45893</v>
@@ -1504,13 +1602,13 @@
       <c r="E10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>106</v>
+      <c r="F10" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H10" s="6">
+        <v>108</v>
+      </c>
+      <c r="H10" s="5">
         <v>45658</v>
       </c>
       <c r="I10" s="2">
@@ -1519,23 +1617,31 @@
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>35490</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>27779</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>48245</v>
       </c>
-      <c r="S10" s="3"/>
-    </row>
-    <row r="11" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+      <c r="N10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="O10" s="5">
+        <v>47324</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2">
         <v>40389</v>
@@ -1546,13 +1652,13 @@
       <c r="E11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>108</v>
+      <c r="F11" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H11" s="6">
+        <v>106</v>
+      </c>
+      <c r="H11" s="5">
         <v>45086</v>
       </c>
       <c r="I11" s="2">
@@ -1561,32 +1667,31 @@
       <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="6">
-        <v>33249</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="K11" s="5">
+        <v>33543</v>
+      </c>
+      <c r="L11" s="5">
         <v>25681</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>46143</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="O11" s="6">
+        <v>111</v>
+      </c>
+      <c r="O11" s="5">
         <v>47324</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2">
         <v>64544</v>
@@ -1597,13 +1702,13 @@
       <c r="E12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>109</v>
+      <c r="F12" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H12" s="6">
+        <v>108</v>
+      </c>
+      <c r="H12" s="5">
         <v>45703</v>
       </c>
       <c r="I12" s="2">
@@ -1612,31 +1717,31 @@
       <c r="J12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>41791</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>32077</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="5">
         <v>52536</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="O12" s="6">
+        <v>114</v>
+      </c>
+      <c r="O12" s="5">
         <v>46937</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="C13" s="2">
         <v>59780</v>
@@ -1647,13 +1752,13 @@
       <c r="E13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>110</v>
+      <c r="F13" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H13" s="6">
+        <v>108</v>
+      </c>
+      <c r="H13" s="5">
         <v>45427</v>
       </c>
       <c r="I13" s="2">
@@ -1662,32 +1767,31 @@
       <c r="J13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>40575</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <v>31758</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>52232</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="O13" s="6">
+        <v>117</v>
+      </c>
+      <c r="O13" s="5">
         <v>47175</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="1:20" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="C14" s="2">
         <v>61489</v>
@@ -1698,13 +1802,13 @@
       <c r="E14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>111</v>
+      <c r="F14" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H14" s="6">
+        <v>108</v>
+      </c>
+      <c r="H14" s="5">
         <v>45427</v>
       </c>
       <c r="I14" s="2">
@@ -1713,32 +1817,31 @@
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>40787</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>33294</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>53752</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="O14" s="6">
+        <v>120</v>
+      </c>
+      <c r="O14" s="5">
         <v>46950</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="C15" s="2">
         <v>72476</v>
@@ -1749,13 +1852,13 @@
       <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>112</v>
+      <c r="F15" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H15" s="6">
+        <v>108</v>
+      </c>
+      <c r="H15" s="5">
         <v>45139</v>
       </c>
       <c r="I15" s="2">
@@ -1764,32 +1867,31 @@
       <c r="J15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L15" s="6">
+      <c r="K15" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L15" s="5">
         <v>34908</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="5">
         <v>55366</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="O15" s="6">
+        <v>123</v>
+      </c>
+      <c r="O15" s="5">
         <v>46950</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S15" s="3"/>
-    </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="C16" s="2">
         <v>56583</v>
@@ -1800,13 +1902,13 @@
       <c r="E16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>112</v>
+      <c r="F16" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H16" s="6">
+        <v>108</v>
+      </c>
+      <c r="H16" s="5">
         <v>45870</v>
       </c>
       <c r="I16" s="2">
@@ -1815,32 +1917,31 @@
       <c r="J16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>40163</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="5">
         <v>32291</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="5">
         <v>52749</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="O16" s="6">
+        <v>125</v>
+      </c>
+      <c r="O16" s="5">
         <v>47114</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="C17" s="2">
         <v>69358</v>
@@ -1851,14 +1952,14 @@
       <c r="E17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>113</v>
+      <c r="F17" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H17" s="6">
-        <v>44927</v>
+        <v>108</v>
+      </c>
+      <c r="H17" s="5">
+        <v>44749</v>
       </c>
       <c r="I17" s="2">
         <v>5</v>
@@ -1866,32 +1967,31 @@
       <c r="J17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L17" s="6">
+      <c r="K17" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L17" s="5">
         <v>35421</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="5">
         <v>55885</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="O17" s="6">
+        <v>128</v>
+      </c>
+      <c r="O17" s="5">
         <v>46433</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S17" s="3"/>
-    </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="C18" s="2">
         <v>69910</v>
@@ -1902,13 +2002,13 @@
       <c r="E18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>113</v>
+      <c r="F18" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H18" s="6">
+        <v>108</v>
+      </c>
+      <c r="H18" s="5">
         <v>45611</v>
       </c>
       <c r="I18" s="2">
@@ -1917,32 +2017,31 @@
       <c r="J18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>42597</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>35095</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="5">
         <v>55550</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="O18" s="6">
+        <v>130</v>
+      </c>
+      <c r="O18" s="5">
         <v>46433</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2">
         <v>75214</v>
@@ -1953,13 +2052,13 @@
       <c r="E19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>113</v>
+      <c r="F19" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H19" s="6">
+        <v>108</v>
+      </c>
+      <c r="H19" s="5">
         <v>45611</v>
       </c>
       <c r="I19" s="2">
@@ -1968,32 +2067,31 @@
       <c r="J19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>44866</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>37127</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>57589</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="O19" s="6">
+        <v>132</v>
+      </c>
+      <c r="O19" s="5">
         <v>46916</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2">
         <v>59785</v>
@@ -2004,13 +2102,13 @@
       <c r="E20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>114</v>
+      <c r="F20" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H20" s="6">
+        <v>135</v>
+      </c>
+      <c r="H20" s="5">
         <v>45627</v>
       </c>
       <c r="I20" s="2">
@@ -2019,40 +2117,40 @@
       <c r="J20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L20" s="6">
+      <c r="K20" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L20" s="5">
         <v>31404</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>51867</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="O20" s="6">
+        <v>136</v>
+      </c>
+      <c r="O20" s="5">
         <v>47175</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>189</v>
+        <v>64</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="R20" s="6">
+        <v>137</v>
+      </c>
+      <c r="R20" s="5">
         <v>47370</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="C21" s="2">
         <v>59784</v>
@@ -2063,13 +2161,13 @@
       <c r="E21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>116</v>
+      <c r="F21" s="7" t="s">
+        <v>139</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H21" s="6">
+        <v>135</v>
+      </c>
+      <c r="H21" s="5">
         <v>45689</v>
       </c>
       <c r="I21" s="2">
@@ -2078,23 +2176,31 @@
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>40575</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <v>31160</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="5">
         <v>51622</v>
       </c>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+      <c r="N21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="O21" s="5">
+        <v>46663</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="C22" s="2">
         <v>62457</v>
@@ -2105,13 +2211,13 @@
       <c r="E22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>117</v>
+      <c r="F22" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H22" s="6">
+        <v>135</v>
+      </c>
+      <c r="H22" s="5">
         <v>45870</v>
       </c>
       <c r="I22" s="2">
@@ -2120,32 +2226,31 @@
       <c r="J22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="6">
-        <v>40917</v>
-      </c>
-      <c r="L22" s="6">
+      <c r="K22" s="5">
+        <v>41153</v>
+      </c>
+      <c r="L22" s="5">
         <v>33911</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="5">
         <v>54393</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="O22" s="6">
+        <v>143</v>
+      </c>
+      <c r="O22" s="5">
         <v>46881</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2">
         <v>69363</v>
@@ -2156,14 +2261,14 @@
       <c r="E23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>118</v>
+      <c r="F23" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H23" s="6">
-        <v>44927</v>
+        <v>135</v>
+      </c>
+      <c r="H23" s="5">
+        <v>44137</v>
       </c>
       <c r="I23" s="2">
         <v>5</v>
@@ -2171,32 +2276,31 @@
       <c r="J23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L23" s="6">
-        <v>34526</v>
-      </c>
-      <c r="M23" s="6">
-        <v>55001</v>
+      <c r="K23" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L23" s="5">
+        <v>34645</v>
+      </c>
+      <c r="M23" s="5">
+        <v>55123</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="O23" s="6">
+        <v>146</v>
+      </c>
+      <c r="O23" s="5">
         <v>46433</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="C24" s="2">
         <v>70891</v>
@@ -2207,14 +2311,14 @@
       <c r="E24" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>118</v>
+      <c r="F24" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H24" s="6">
-        <v>44927</v>
+        <v>135</v>
+      </c>
+      <c r="H24" s="5">
+        <v>44749</v>
       </c>
       <c r="I24" s="2">
         <v>5</v>
@@ -2222,32 +2326,31 @@
       <c r="J24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>42725</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="5">
         <v>34362</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="5">
         <v>54820</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="O24" s="6">
+        <v>148</v>
+      </c>
+      <c r="O24" s="5">
         <v>46433</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>68</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2">
         <v>78112</v>
@@ -2256,15 +2359,15 @@
         <v>33</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>119</v>
+        <v>65</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>150</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H25" s="6">
+        <v>135</v>
+      </c>
+      <c r="H25" s="5">
         <v>45962</v>
       </c>
       <c r="I25" s="2">
@@ -2273,23 +2376,22 @@
       <c r="J25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <v>45962</v>
       </c>
-      <c r="L25" s="6">
-        <v>46084</v>
-      </c>
-      <c r="M25" s="6">
-        <v>20455</v>
-      </c>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+      <c r="L25" s="5">
+        <v>37315</v>
+      </c>
+      <c r="M25" s="5">
+        <v>57770</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="C26" s="2">
         <v>59783</v>
@@ -2300,13 +2402,13 @@
       <c r="E26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>119</v>
+      <c r="F26" s="7" t="s">
+        <v>150</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H26" s="6">
+        <v>135</v>
+      </c>
+      <c r="H26" s="5">
         <v>45611</v>
       </c>
       <c r="I26" s="2">
@@ -2315,32 +2417,31 @@
       <c r="J26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L26" s="6">
-        <v>29110</v>
-      </c>
-      <c r="M26" s="6">
-        <v>49583</v>
+      <c r="K26" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L26" s="5">
+        <v>29198</v>
+      </c>
+      <c r="M26" s="5">
+        <v>49675</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="O26" s="6">
+        <v>152</v>
+      </c>
+      <c r="O26" s="5">
         <v>46610</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="C27" s="2">
         <v>44185</v>
@@ -2351,13 +2452,13 @@
       <c r="E27" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>120</v>
+      <c r="F27" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H27" s="6">
+        <v>155</v>
+      </c>
+      <c r="H27" s="5">
         <v>45427</v>
       </c>
       <c r="I27" s="2">
@@ -2366,31 +2467,31 @@
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>35217</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>28103</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="5">
         <v>48580</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="O27" s="6">
+        <v>156</v>
+      </c>
+      <c r="O27" s="5">
         <v>47203</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="C28" s="2">
         <v>61512</v>
@@ -2401,13 +2502,13 @@
       <c r="E28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>122</v>
+      <c r="F28" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" s="6">
+        <v>155</v>
+      </c>
+      <c r="H28" s="5">
         <v>45611</v>
       </c>
       <c r="I28" s="2">
@@ -2416,32 +2517,31 @@
       <c r="J28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>40787</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>34129</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>54605</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="O28" s="6">
+        <v>159</v>
+      </c>
+      <c r="O28" s="5">
         <v>47175</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="C29" s="2">
         <v>53584</v>
@@ -2452,13 +2552,13 @@
       <c r="E29" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>123</v>
+      <c r="F29" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H29" s="6">
+        <v>155</v>
+      </c>
+      <c r="H29" s="5">
         <v>45870</v>
       </c>
       <c r="I29" s="2">
@@ -2467,32 +2567,31 @@
       <c r="J29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>39814</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="5">
         <v>32125</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="5">
         <v>52597</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="O29" s="6">
+        <v>162</v>
+      </c>
+      <c r="O29" s="5">
         <v>47203</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="C30" s="2">
         <v>77881</v>
@@ -2501,15 +2600,15 @@
         <v>33</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>124</v>
+        <v>69</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>164</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H30" s="6">
+        <v>155</v>
+      </c>
+      <c r="H30" s="5">
         <v>45809</v>
       </c>
       <c r="I30" s="2">
@@ -2518,23 +2617,22 @@
       <c r="J30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>45689</v>
       </c>
-      <c r="L30" s="6">
-        <v>46084</v>
-      </c>
-      <c r="M30" s="6">
-        <v>20455</v>
-      </c>
-      <c r="S30" s="3"/>
-    </row>
-    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+      <c r="L30" s="5">
+        <v>38646</v>
+      </c>
+      <c r="M30" s="5">
+        <v>59111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="C31" s="2">
         <v>77888</v>
@@ -2543,15 +2641,15 @@
         <v>33</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>124</v>
+        <v>69</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>164</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="6">
+        <v>155</v>
+      </c>
+      <c r="H31" s="5">
         <v>45809</v>
       </c>
       <c r="I31" s="2">
@@ -2560,23 +2658,22 @@
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="5">
         <v>45689</v>
       </c>
-      <c r="L31" s="6">
-        <v>46084</v>
-      </c>
-      <c r="M31" s="6">
-        <v>20455</v>
-      </c>
-      <c r="S31" s="3"/>
-    </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+      <c r="L31" s="5">
+        <v>36820</v>
+      </c>
+      <c r="M31" s="5">
+        <v>57285</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="C32" s="2">
         <v>70893</v>
@@ -2587,14 +2684,14 @@
       <c r="E32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>124</v>
+      <c r="F32" s="7" t="s">
+        <v>164</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H32" s="6">
-        <v>44927</v>
+        <v>155</v>
+      </c>
+      <c r="H32" s="5">
+        <v>43322</v>
       </c>
       <c r="I32" s="2">
         <v>5</v>
@@ -2602,23 +2699,31 @@
       <c r="J32" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>42725</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="5">
         <v>35429</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="5">
         <v>55885</v>
       </c>
-      <c r="S32" s="3"/>
-    </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+      <c r="N32" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="O32" s="5">
+        <v>46433</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="C33" s="2">
         <v>59787</v>
@@ -2629,14 +2734,14 @@
       <c r="E33" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>124</v>
+      <c r="F33" s="7" t="s">
+        <v>164</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H33" s="6">
-        <v>44927</v>
+        <v>155</v>
+      </c>
+      <c r="H33" s="5">
+        <v>44749</v>
       </c>
       <c r="I33" s="2">
         <v>5</v>
@@ -2644,32 +2749,31 @@
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K33" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L33" s="6">
+      <c r="K33" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L33" s="5">
         <v>29602</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="5">
         <v>50072</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O33" s="6">
+        <v>169</v>
+      </c>
+      <c r="O33" s="5">
         <v>47265</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S33" s="3"/>
-    </row>
-    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2">
         <v>69351</v>
@@ -2680,13 +2784,13 @@
       <c r="E34" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>125</v>
+      <c r="F34" s="7" t="s">
+        <v>171</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H34" s="6">
+        <v>155</v>
+      </c>
+      <c r="H34" s="5">
         <v>45611</v>
       </c>
       <c r="I34" s="2">
@@ -2695,32 +2799,31 @@
       <c r="J34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L34" s="6">
+      <c r="K34" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L34" s="5">
         <v>35842</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <v>56309</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="O34" s="6">
+        <v>172</v>
+      </c>
+      <c r="O34" s="5">
         <v>46446</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S34" s="3"/>
-    </row>
-    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2">
         <v>45867</v>
@@ -2731,13 +2834,13 @@
       <c r="E35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>126</v>
+      <c r="F35" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H35" s="6">
+        <v>175</v>
+      </c>
+      <c r="H35" s="5">
         <v>45427</v>
       </c>
       <c r="I35" s="2">
@@ -2746,22 +2849,31 @@
       <c r="J35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="5">
         <v>35490</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="5">
         <v>26516</v>
       </c>
-      <c r="M35" s="6">
+      <c r="M35" s="5">
         <v>46997</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+      <c r="N35" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="O35" s="5">
+        <v>47203</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="C36" s="2">
         <v>61500</v>
@@ -2772,13 +2884,13 @@
       <c r="E36" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>128</v>
+      <c r="F36" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H36" s="6">
+        <v>175</v>
+      </c>
+      <c r="H36" s="5">
         <v>45870</v>
       </c>
       <c r="I36" s="2">
@@ -2787,23 +2899,31 @@
       <c r="J36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K36" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L36" s="6">
+      <c r="K36" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L36" s="5">
         <v>33997</v>
       </c>
-      <c r="M36" s="6">
+      <c r="M36" s="5">
         <v>54455</v>
       </c>
-      <c r="S36" s="3"/>
-    </row>
-    <row r="37" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+      <c r="N36" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="O36" s="5">
+        <v>47175</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="C37" s="2">
         <v>69367</v>
@@ -2814,13 +2934,13 @@
       <c r="E37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>129</v>
+      <c r="F37" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H37" s="6">
+        <v>175</v>
+      </c>
+      <c r="H37" s="5">
         <v>45731</v>
       </c>
       <c r="I37" s="2">
@@ -2829,32 +2949,31 @@
       <c r="J37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L37" s="6">
-        <v>35106</v>
-      </c>
-      <c r="M37" s="6">
-        <v>55579</v>
+      <c r="K37" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L37" s="5">
+        <v>35371</v>
+      </c>
+      <c r="M37" s="5">
+        <v>55854</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="O37" s="6">
+        <v>182</v>
+      </c>
+      <c r="O37" s="5">
         <v>46446</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S37" s="3"/>
-    </row>
-    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2">
         <v>48084</v>
@@ -2865,14 +2984,14 @@
       <c r="E38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>130</v>
+      <c r="F38" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H38" s="6">
-        <v>44927</v>
+        <v>175</v>
+      </c>
+      <c r="H38" s="5">
+        <v>42005</v>
       </c>
       <c r="I38" s="2">
         <v>5</v>
@@ -2880,32 +2999,31 @@
       <c r="J38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K38" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L38" s="6">
-        <v>26831</v>
-      </c>
-      <c r="M38" s="6">
+      <c r="K38" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L38" s="5">
+        <v>26832</v>
+      </c>
+      <c r="M38" s="5">
         <v>47300</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="O38" s="6">
+        <v>185</v>
+      </c>
+      <c r="O38" s="5">
         <v>47175</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S38" s="3"/>
-    </row>
-    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="C39" s="2">
         <v>70404</v>
@@ -2916,13 +3034,13 @@
       <c r="E39" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>130</v>
+      <c r="F39" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H39" s="6">
+        <v>175</v>
+      </c>
+      <c r="H39" s="5">
         <v>45870</v>
       </c>
       <c r="I39" s="2">
@@ -2931,32 +3049,31 @@
       <c r="J39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K39" s="6">
-        <v>42380</v>
-      </c>
-      <c r="L39" s="6">
+      <c r="K39" s="5">
+        <v>42675</v>
+      </c>
+      <c r="L39" s="5">
         <v>35539</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M39" s="5">
         <v>56005</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="O39" s="6">
+        <v>187</v>
+      </c>
+      <c r="O39" s="5">
         <v>46476</v>
       </c>
       <c r="P39" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="C40" s="2">
         <v>69911</v>
@@ -2967,14 +3084,14 @@
       <c r="E40" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>131</v>
+      <c r="F40" s="7" t="s">
+        <v>189</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H40" s="6">
-        <v>44927</v>
+        <v>175</v>
+      </c>
+      <c r="H40" s="5">
+        <v>44348</v>
       </c>
       <c r="I40" s="2">
         <v>5</v>
@@ -2982,32 +3099,31 @@
       <c r="J40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="5">
         <v>42597</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="5">
         <v>33497</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40" s="5">
         <v>53966</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="O40" s="6">
+        <v>190</v>
+      </c>
+      <c r="O40" s="5">
         <v>46433</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="C41" s="2">
         <v>53634</v>
@@ -3018,13 +3134,13 @@
       <c r="E41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>132</v>
+      <c r="F41" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H41" s="6">
+        <v>193</v>
+      </c>
+      <c r="H41" s="5">
         <v>45870</v>
       </c>
       <c r="I41" s="2">
@@ -3033,31 +3149,31 @@
       <c r="J41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="5">
         <v>39814</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="5">
         <v>32817</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="5">
         <v>53297</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="O41" s="6">
+        <v>194</v>
+      </c>
+      <c r="O41" s="5">
         <v>47114</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="C42" s="2">
         <v>61493</v>
@@ -3068,13 +3184,13 @@
       <c r="E42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>134</v>
+      <c r="F42" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H42" s="6">
+        <v>193</v>
+      </c>
+      <c r="H42" s="5">
         <v>45611</v>
       </c>
       <c r="I42" s="2">
@@ -3083,32 +3199,31 @@
       <c r="J42" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L42" s="6">
-        <v>33855</v>
-      </c>
-      <c r="M42" s="6">
-        <v>54332</v>
+      <c r="K42" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L42" s="5">
+        <v>33825</v>
+      </c>
+      <c r="M42" s="5">
+        <v>54302</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="O42" s="6">
+        <v>197</v>
+      </c>
+      <c r="O42" s="5">
         <v>47324</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S42" s="3"/>
-    </row>
-    <row r="43" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>86</v>
+        <v>198</v>
       </c>
       <c r="C43" s="2">
         <v>61511</v>
@@ -3119,13 +3234,13 @@
       <c r="E43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>135</v>
+      <c r="F43" s="7" t="s">
+        <v>199</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H43" s="6">
+        <v>193</v>
+      </c>
+      <c r="H43" s="5">
         <v>45689</v>
       </c>
       <c r="I43" s="2">
@@ -3134,32 +3249,31 @@
       <c r="J43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K43" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L43" s="6">
-        <v>34156</v>
-      </c>
-      <c r="M43" s="6">
-        <v>54636</v>
+      <c r="K43" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L43" s="5">
+        <v>34127</v>
+      </c>
+      <c r="M43" s="5">
+        <v>54605</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="O43" s="6">
+        <v>200</v>
+      </c>
+      <c r="O43" s="5">
         <v>47114</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S43" s="3"/>
-    </row>
-    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="C44" s="2">
         <v>77948</v>
@@ -3168,15 +3282,15 @@
         <v>33</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>136</v>
+        <v>69</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H44" s="6">
+        <v>193</v>
+      </c>
+      <c r="H44" s="5">
         <v>45809</v>
       </c>
       <c r="I44" s="2">
@@ -3185,23 +3299,22 @@
       <c r="J44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K44" s="6">
+      <c r="K44" s="5">
         <v>45689</v>
       </c>
-      <c r="L44" s="6">
-        <v>46084</v>
-      </c>
-      <c r="M44" s="6">
-        <v>20455</v>
-      </c>
-      <c r="S44" s="3"/>
-    </row>
-    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+      <c r="L44" s="5">
+        <v>36986</v>
+      </c>
+      <c r="M44" s="5">
+        <v>57466</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="C45" s="2">
         <v>77943</v>
@@ -3210,15 +3323,15 @@
         <v>33</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>136</v>
+        <v>69</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H45" s="6">
+        <v>193</v>
+      </c>
+      <c r="H45" s="5">
         <v>45809</v>
       </c>
       <c r="I45" s="2">
@@ -3227,23 +3340,22 @@
       <c r="J45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="5">
         <v>45689</v>
       </c>
-      <c r="L45" s="6">
-        <v>46084</v>
-      </c>
-      <c r="M45" s="6">
-        <v>20455</v>
-      </c>
-      <c r="S45" s="3"/>
-    </row>
-    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+      <c r="L45" s="5">
+        <v>37896</v>
+      </c>
+      <c r="M45" s="5">
+        <v>58380</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>89</v>
+        <v>204</v>
       </c>
       <c r="C46" s="2">
         <v>70892</v>
@@ -3254,13 +3366,13 @@
       <c r="E46" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>137</v>
+      <c r="F46" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H46" s="6">
+        <v>193</v>
+      </c>
+      <c r="H46" s="5">
         <v>45611</v>
       </c>
       <c r="I46" s="2">
@@ -3269,32 +3381,31 @@
       <c r="J46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="5">
         <v>42725</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="5">
         <v>35459</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="5">
         <v>55916</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="O46" s="6">
+        <v>206</v>
+      </c>
+      <c r="O46" s="5">
         <v>46433</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="S46" s="3"/>
-    </row>
-    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="C47" s="2">
         <v>53633</v>
@@ -3305,13 +3416,13 @@
       <c r="E47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>138</v>
+      <c r="F47" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H47" s="6">
+        <v>209</v>
+      </c>
+      <c r="H47" s="5">
         <v>45870</v>
       </c>
       <c r="I47" s="2">
@@ -3320,40 +3431,40 @@
       <c r="J47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="5">
         <v>39814</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="5">
         <v>32815</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47" s="5">
         <v>53297</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="O47" s="6">
+        <v>210</v>
+      </c>
+      <c r="O47" s="5">
         <v>47114</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>189</v>
+        <v>64</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="R47" s="6">
+        <v>211</v>
+      </c>
+      <c r="R47" s="5">
         <v>47370</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>91</v>
+        <v>212</v>
       </c>
       <c r="C48" s="2">
         <v>56584</v>
@@ -3364,13 +3475,13 @@
       <c r="E48" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>140</v>
+      <c r="F48" s="7" t="s">
+        <v>213</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H48" s="6">
+        <v>209</v>
+      </c>
+      <c r="H48" s="5">
         <v>45731</v>
       </c>
       <c r="I48" s="2">
@@ -3379,23 +3490,31 @@
       <c r="J48" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="5">
         <v>40163</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="5">
         <v>32512</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48" s="5">
         <v>52994</v>
       </c>
-      <c r="S48" s="3"/>
-    </row>
-    <row r="49" spans="1:18" s="3" customFormat="1" ht="26.25" hidden="1" x14ac:dyDescent="0.45">
+      <c r="N48" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="O48" s="5">
+        <v>47114</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>92</v>
+        <v>215</v>
       </c>
       <c r="C49" s="2">
         <v>56586</v>
@@ -3406,13 +3525,13 @@
       <c r="E49" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>141</v>
+      <c r="F49" s="7" t="s">
+        <v>216</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H49" s="6">
+        <v>209</v>
+      </c>
+      <c r="H49" s="5">
         <v>45427</v>
       </c>
       <c r="I49" s="2">
@@ -3421,33 +3540,31 @@
       <c r="J49" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="5">
         <v>40163</v>
       </c>
-      <c r="L49" s="6">
-        <v>32664</v>
-      </c>
-      <c r="M49" s="6">
+      <c r="L49" s="5">
+        <v>32665</v>
+      </c>
+      <c r="M49" s="5">
         <v>53144</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="O49" s="6">
+        <v>217</v>
+      </c>
+      <c r="O49" s="5">
         <v>47324</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="6"/>
-    </row>
-    <row r="50" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>93</v>
+        <v>218</v>
       </c>
       <c r="C50" s="2">
         <v>70401</v>
@@ -3458,14 +3575,14 @@
       <c r="E50" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>142</v>
+      <c r="F50" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H50" s="6">
-        <v>44927</v>
+        <v>209</v>
+      </c>
+      <c r="H50" s="5">
+        <v>44197</v>
       </c>
       <c r="I50" s="2">
         <v>5</v>
@@ -3473,33 +3590,31 @@
       <c r="J50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K50" s="6">
-        <v>42380</v>
-      </c>
-      <c r="L50" s="6">
+      <c r="K50" s="5">
+        <v>42675</v>
+      </c>
+      <c r="L50" s="5">
         <v>33905</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M50" s="5">
         <v>54363</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="O50" s="6">
+        <v>220</v>
+      </c>
+      <c r="O50" s="5">
         <v>46837</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="6"/>
-    </row>
-    <row r="51" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>94</v>
+        <v>221</v>
       </c>
       <c r="C51" s="2">
         <v>69912</v>
@@ -3510,14 +3625,14 @@
       <c r="E51" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>142</v>
+      <c r="F51" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H51" s="6">
-        <v>44927</v>
+        <v>209</v>
+      </c>
+      <c r="H51" s="5">
+        <v>45992</v>
       </c>
       <c r="I51" s="2">
         <v>5</v>
@@ -3525,33 +3640,31 @@
       <c r="J51" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K51" s="6">
+      <c r="K51" s="5">
         <v>42597</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51" s="5">
         <v>35843</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51" s="5">
         <v>56309</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="O51" s="6">
+        <v>222</v>
+      </c>
+      <c r="O51" s="5">
         <v>46433</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" s="6"/>
-    </row>
-    <row r="52" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>95</v>
+        <v>223</v>
       </c>
       <c r="C52" s="2">
         <v>59786</v>
@@ -3562,13 +3675,13 @@
       <c r="E52" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>142</v>
+      <c r="F52" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H52" s="6">
+        <v>209</v>
+      </c>
+      <c r="H52" s="5">
         <v>45611</v>
       </c>
       <c r="I52" s="2">
@@ -3577,33 +3690,31 @@
       <c r="J52" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K52" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L52" s="6">
+      <c r="K52" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L52" s="5">
         <v>32067</v>
       </c>
-      <c r="M52" s="6">
+      <c r="M52" s="5">
         <v>52536</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="O52" s="6">
+        <v>224</v>
+      </c>
+      <c r="O52" s="5">
         <v>47114</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" s="6"/>
-    </row>
-    <row r="53" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="C53" s="2">
         <v>77811</v>
@@ -3612,15 +3723,15 @@
         <v>33</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>187</v>
+        <v>69</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H53" s="6">
+        <v>209</v>
+      </c>
+      <c r="H53" s="5">
         <v>45809</v>
       </c>
       <c r="I53" s="2">
@@ -3629,765 +3740,205 @@
       <c r="J53" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K53" s="6">
+      <c r="K53" s="5">
         <v>45689</v>
       </c>
-      <c r="L53" s="6">
-        <v>46084</v>
-      </c>
-      <c r="M53" s="6">
-        <v>20455</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
-      <c r="R53" s="6"/>
-    </row>
-    <row r="54" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="6"/>
-      <c r="Q54" s="2"/>
-      <c r="R54" s="6"/>
-    </row>
-    <row r="55" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="6"/>
-      <c r="Q55" s="2"/>
-      <c r="R55" s="6"/>
-    </row>
-    <row r="56" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="6"/>
-      <c r="Q56" s="2"/>
-      <c r="R56" s="6"/>
-    </row>
-    <row r="57" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="6"/>
-      <c r="Q57" s="2"/>
-      <c r="R57" s="6"/>
-    </row>
-    <row r="58" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="6"/>
-      <c r="Q58" s="2"/>
-      <c r="R58" s="6"/>
-    </row>
-    <row r="59" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="6"/>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="6"/>
-    </row>
-    <row r="60" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="6"/>
-      <c r="Q60" s="2"/>
-      <c r="R60" s="6"/>
-    </row>
-    <row r="61" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="2"/>
-      <c r="O61" s="6"/>
-      <c r="Q61" s="2"/>
-      <c r="R61" s="6"/>
-    </row>
-    <row r="62" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
-      <c r="N62" s="2"/>
-      <c r="O62" s="6"/>
-      <c r="Q62" s="2"/>
-      <c r="R62" s="6"/>
-    </row>
-    <row r="63" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="6"/>
-      <c r="Q63" s="2"/>
-      <c r="R63" s="6"/>
-    </row>
-    <row r="64" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
-      <c r="N64" s="2"/>
-      <c r="O64" s="6"/>
-      <c r="Q64" s="2"/>
-      <c r="R64" s="6"/>
-    </row>
-    <row r="65" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6"/>
-      <c r="N65" s="2"/>
-      <c r="O65" s="6"/>
-      <c r="Q65" s="2"/>
-      <c r="R65" s="6"/>
-    </row>
-    <row r="66" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
-      <c r="N66" s="2"/>
-      <c r="O66" s="6"/>
-      <c r="Q66" s="2"/>
-      <c r="R66" s="6"/>
-    </row>
-    <row r="67" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
-      <c r="M67" s="6"/>
-      <c r="N67" s="2"/>
-      <c r="O67" s="6"/>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="6"/>
-    </row>
-    <row r="68" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
-      <c r="M68" s="6"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="6"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="6"/>
-    </row>
-    <row r="69" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
-      <c r="M69" s="6"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="6"/>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="6"/>
-    </row>
-    <row r="70" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
-      <c r="M70" s="6"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="6"/>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="6"/>
-    </row>
-    <row r="71" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
-      <c r="M71" s="6"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="6"/>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="6"/>
-    </row>
-    <row r="72" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="6"/>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="6"/>
-    </row>
-    <row r="73" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
-      <c r="M73" s="6"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="6"/>
-      <c r="Q73" s="2"/>
-      <c r="R73" s="6"/>
-    </row>
-    <row r="74" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="6"/>
-      <c r="Q74" s="2"/>
-      <c r="R74" s="6"/>
-    </row>
-    <row r="75" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="6"/>
-      <c r="Q75" s="2"/>
-      <c r="R75" s="6"/>
-    </row>
-    <row r="76" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="6"/>
-      <c r="M76" s="6"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="6"/>
-      <c r="Q76" s="2"/>
-      <c r="R76" s="6"/>
-    </row>
-    <row r="77" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
-      <c r="M77" s="6"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="6"/>
-      <c r="Q77" s="2"/>
-      <c r="R77" s="6"/>
-    </row>
-    <row r="78" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
-      <c r="M78" s="6"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="6"/>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="6"/>
-    </row>
-    <row r="79" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-      <c r="M79" s="6"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="6"/>
-      <c r="Q79" s="2"/>
-      <c r="R79" s="6"/>
-    </row>
-    <row r="80" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-      <c r="M80" s="6"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="6"/>
-      <c r="Q80" s="2"/>
-      <c r="R80" s="6"/>
-    </row>
-    <row r="81" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-      <c r="M81" s="6"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="6"/>
-      <c r="Q81" s="2"/>
-      <c r="R81" s="6"/>
-    </row>
-    <row r="82" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
-      <c r="M82" s="6"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="6"/>
-      <c r="Q82" s="2"/>
-      <c r="R82" s="6"/>
-    </row>
-    <row r="83" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
-      <c r="M83" s="6"/>
-      <c r="N83" s="2"/>
-      <c r="O83" s="6"/>
-      <c r="Q83" s="2"/>
-      <c r="R83" s="6"/>
-    </row>
-    <row r="84" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
-      <c r="M84" s="6"/>
-      <c r="N84" s="2"/>
-      <c r="O84" s="6"/>
-      <c r="Q84" s="2"/>
-      <c r="R84" s="6"/>
-    </row>
-    <row r="85" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
-      <c r="M85" s="6"/>
-      <c r="N85" s="2"/>
-      <c r="O85" s="6"/>
-      <c r="Q85" s="2"/>
-      <c r="R85" s="6"/>
-    </row>
-    <row r="86" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
-      <c r="M86" s="6"/>
-      <c r="N86" s="2"/>
-      <c r="O86" s="6"/>
-      <c r="Q86" s="2"/>
-      <c r="R86" s="6"/>
-    </row>
-    <row r="87" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
-      <c r="M87" s="6"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="6"/>
-      <c r="Q87" s="2"/>
-      <c r="R87" s="6"/>
-    </row>
-    <row r="88" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
-      <c r="M88" s="6"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="6"/>
-      <c r="Q88" s="2"/>
-      <c r="R88" s="6"/>
-    </row>
-    <row r="89" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="6"/>
-      <c r="M89" s="6"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="6"/>
-      <c r="Q89" s="2"/>
-      <c r="R89" s="6"/>
-    </row>
-    <row r="90" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="6"/>
-      <c r="M90" s="6"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="6"/>
-      <c r="Q90" s="2"/>
-      <c r="R90" s="6"/>
-    </row>
-    <row r="91" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="6"/>
-      <c r="M91" s="6"/>
-      <c r="N91" s="2"/>
-      <c r="O91" s="6"/>
-      <c r="Q91" s="2"/>
-      <c r="R91" s="6"/>
-    </row>
-    <row r="92" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
-      <c r="M92" s="6"/>
-      <c r="N92" s="2"/>
-      <c r="O92" s="6"/>
-      <c r="Q92" s="2"/>
-      <c r="R92" s="6"/>
-    </row>
-    <row r="93" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
-      <c r="M93" s="6"/>
-      <c r="N93" s="2"/>
-      <c r="O93" s="6"/>
-      <c r="Q93" s="2"/>
-      <c r="R93" s="6"/>
-    </row>
-    <row r="94" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
-      <c r="M94" s="6"/>
-      <c r="N94" s="2"/>
-      <c r="O94" s="6"/>
-      <c r="Q94" s="2"/>
-      <c r="R94" s="6"/>
-    </row>
+      <c r="L53" s="5">
+        <v>37406</v>
+      </c>
+      <c r="M53" s="5">
+        <v>57862</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="65" x14ac:dyDescent="0.45"/>
+    <row r="66" x14ac:dyDescent="0.45"/>
+    <row r="67" x14ac:dyDescent="0.45"/>
+    <row r="68" x14ac:dyDescent="0.45"/>
+    <row r="69" x14ac:dyDescent="0.45"/>
+    <row r="70" x14ac:dyDescent="0.45"/>
+    <row r="71" x14ac:dyDescent="0.45"/>
+    <row r="72" x14ac:dyDescent="0.45"/>
+    <row r="73" x14ac:dyDescent="0.45"/>
+    <row r="74" x14ac:dyDescent="0.45"/>
+    <row r="75" x14ac:dyDescent="0.45"/>
+    <row r="76" x14ac:dyDescent="0.45"/>
+    <row r="77" x14ac:dyDescent="0.45"/>
+    <row r="78" x14ac:dyDescent="0.45"/>
+    <row r="79" x14ac:dyDescent="0.45"/>
+    <row r="80" x14ac:dyDescent="0.45"/>
+    <row r="81" x14ac:dyDescent="0.45"/>
+    <row r="82" x14ac:dyDescent="0.45"/>
+    <row r="83" x14ac:dyDescent="0.45"/>
+    <row r="84" x14ac:dyDescent="0.45"/>
+    <row r="85" x14ac:dyDescent="0.45"/>
+    <row r="86" x14ac:dyDescent="0.45"/>
+    <row r="87" x14ac:dyDescent="0.45"/>
+    <row r="88" x14ac:dyDescent="0.45"/>
+    <row r="89" x14ac:dyDescent="0.45"/>
+    <row r="90" x14ac:dyDescent="0.45"/>
+    <row r="91" x14ac:dyDescent="0.45"/>
+    <row r="92" x14ac:dyDescent="0.45"/>
+    <row r="93" x14ac:dyDescent="0.45"/>
+    <row r="94" x14ac:dyDescent="0.45"/>
+    <row r="95" x14ac:dyDescent="0.45"/>
+    <row r="96" x14ac:dyDescent="0.45"/>
+    <row r="97" x14ac:dyDescent="0.45"/>
+    <row r="98" x14ac:dyDescent="0.45"/>
+    <row r="99" x14ac:dyDescent="0.45"/>
+    <row r="100" x14ac:dyDescent="0.45"/>
+    <row r="101" x14ac:dyDescent="0.45"/>
+    <row r="102" x14ac:dyDescent="0.45"/>
+    <row r="103" x14ac:dyDescent="0.45"/>
+    <row r="104" x14ac:dyDescent="0.45"/>
+    <row r="105" x14ac:dyDescent="0.45"/>
+    <row r="106" x14ac:dyDescent="0.45"/>
+    <row r="107" x14ac:dyDescent="0.45"/>
+    <row r="108" x14ac:dyDescent="0.45"/>
+    <row r="109" x14ac:dyDescent="0.45"/>
+    <row r="110" x14ac:dyDescent="0.45"/>
+    <row r="111" x14ac:dyDescent="0.45"/>
+    <row r="112" x14ac:dyDescent="0.45"/>
+    <row r="113" x14ac:dyDescent="0.45"/>
+    <row r="114" x14ac:dyDescent="0.45"/>
+    <row r="115" x14ac:dyDescent="0.45"/>
+    <row r="116" x14ac:dyDescent="0.45"/>
+    <row r="117" x14ac:dyDescent="0.45"/>
+    <row r="118" x14ac:dyDescent="0.45"/>
+    <row r="119" x14ac:dyDescent="0.45"/>
+    <row r="120" x14ac:dyDescent="0.45"/>
+    <row r="121" x14ac:dyDescent="0.45"/>
+    <row r="122" x14ac:dyDescent="0.45"/>
+    <row r="123" x14ac:dyDescent="0.45"/>
+    <row r="124" x14ac:dyDescent="0.45"/>
+    <row r="125" x14ac:dyDescent="0.45"/>
+    <row r="126" x14ac:dyDescent="0.45"/>
+    <row r="127" x14ac:dyDescent="0.45"/>
+    <row r="128" x14ac:dyDescent="0.45"/>
+    <row r="129" x14ac:dyDescent="0.45"/>
+    <row r="130" x14ac:dyDescent="0.45"/>
+    <row r="131" x14ac:dyDescent="0.45"/>
+    <row r="132" x14ac:dyDescent="0.45"/>
+    <row r="133" x14ac:dyDescent="0.45"/>
+    <row r="134" x14ac:dyDescent="0.45"/>
+    <row r="135" x14ac:dyDescent="0.45"/>
+    <row r="136" x14ac:dyDescent="0.45"/>
+    <row r="137" x14ac:dyDescent="0.45"/>
+    <row r="138" x14ac:dyDescent="0.45"/>
+    <row r="139" x14ac:dyDescent="0.45"/>
+    <row r="140" x14ac:dyDescent="0.45"/>
+    <row r="141" x14ac:dyDescent="0.45"/>
+    <row r="142" x14ac:dyDescent="0.45"/>
+    <row r="143" x14ac:dyDescent="0.45"/>
+    <row r="144" x14ac:dyDescent="0.45"/>
+    <row r="145" x14ac:dyDescent="0.45"/>
+    <row r="146" x14ac:dyDescent="0.45"/>
+    <row r="147" x14ac:dyDescent="0.45"/>
+    <row r="148" x14ac:dyDescent="0.45"/>
+    <row r="149" x14ac:dyDescent="0.45"/>
+    <row r="150" x14ac:dyDescent="0.45"/>
+    <row r="151" x14ac:dyDescent="0.45"/>
+    <row r="152" x14ac:dyDescent="0.45"/>
+    <row r="153" x14ac:dyDescent="0.45"/>
+    <row r="154" x14ac:dyDescent="0.45"/>
+    <row r="155" x14ac:dyDescent="0.45"/>
+    <row r="156" x14ac:dyDescent="0.45"/>
+    <row r="157" x14ac:dyDescent="0.45"/>
+    <row r="158" x14ac:dyDescent="0.45"/>
+    <row r="159" x14ac:dyDescent="0.45"/>
+    <row r="160" x14ac:dyDescent="0.45"/>
+    <row r="161" x14ac:dyDescent="0.45"/>
+    <row r="162" x14ac:dyDescent="0.45"/>
+    <row r="163" x14ac:dyDescent="0.45"/>
+    <row r="164" x14ac:dyDescent="0.45"/>
+    <row r="165" x14ac:dyDescent="0.45"/>
+    <row r="166" x14ac:dyDescent="0.45"/>
+    <row r="167" x14ac:dyDescent="0.45"/>
+    <row r="168" x14ac:dyDescent="0.45"/>
+    <row r="169" x14ac:dyDescent="0.45"/>
+    <row r="170" x14ac:dyDescent="0.45"/>
+    <row r="171" x14ac:dyDescent="0.45"/>
+    <row r="172" x14ac:dyDescent="0.45"/>
+    <row r="173" x14ac:dyDescent="0.45"/>
+    <row r="174" x14ac:dyDescent="0.45"/>
+    <row r="175" x14ac:dyDescent="0.45"/>
+    <row r="176" x14ac:dyDescent="0.45"/>
+    <row r="177" x14ac:dyDescent="0.45"/>
+    <row r="178" x14ac:dyDescent="0.45"/>
+    <row r="179" x14ac:dyDescent="0.45"/>
+    <row r="180" x14ac:dyDescent="0.45"/>
+    <row r="181" x14ac:dyDescent="0.45"/>
+    <row r="182" x14ac:dyDescent="0.45"/>
+    <row r="183" x14ac:dyDescent="0.45"/>
+    <row r="184" x14ac:dyDescent="0.45"/>
+    <row r="185" x14ac:dyDescent="0.45"/>
+    <row r="186" x14ac:dyDescent="0.45"/>
+    <row r="187" x14ac:dyDescent="0.45"/>
+    <row r="188" x14ac:dyDescent="0.45"/>
+    <row r="189" x14ac:dyDescent="0.45"/>
+    <row r="190" x14ac:dyDescent="0.45"/>
+    <row r="191" x14ac:dyDescent="0.45"/>
+    <row r="192" x14ac:dyDescent="0.45"/>
+    <row r="193" x14ac:dyDescent="0.45"/>
+    <row r="194" x14ac:dyDescent="0.45"/>
+    <row r="195" x14ac:dyDescent="0.45"/>
+    <row r="196" x14ac:dyDescent="0.45"/>
+    <row r="197" x14ac:dyDescent="0.45"/>
+    <row r="198" x14ac:dyDescent="0.45"/>
+    <row r="199" x14ac:dyDescent="0.45"/>
+    <row r="200" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A1:T94" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="QC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T199" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D996</xm:sqref>
+          <xm:sqref>D2:D986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J996</xm:sqref>
+          <xm:sqref>J2:J986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I996</xm:sqref>
+          <xm:sqref>I2:I986</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{354EFE19-C43E-4A2D-83B1-FD15C013476E}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DE71029-D453-4F4E-B557-CC5A72AEA9EB}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P200 S2:S200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262E53F9-7911-451D-88C9-1E420930ED84}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$F:$F</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4397,130 +3948,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" style="8" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="4" width="14.46484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="49.53125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="D4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="D9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="D10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="8">
         <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
